--- a/consent_forms/030_tattoo_aftercare_guidelines_acknowledgment--consent_forms.xlsx
+++ b/consent_forms/030_tattoo_aftercare_guidelines_acknowledgment--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="47" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,20 +515,24 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>tattoo_aftercare_guidelines_acknowledgment</t>
+          <t>accept_tattoo_aftercare_guidelines</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>i_accept_to_follow_tattoo_aftercare_guidelines</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Do you accept to follow tattoo aftercare guidelines?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please check this box if you understand and agree to follow the aftercare guidelines.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>yes</t>
@@ -538,20 +542,24 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>i_understand_tattoo_aftercare_guidelines</t>
+          <t>understand_aftercare_guidelines</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>do_you_understand_tattoo_aftercare_guidelines</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Do you understand tattoo aftercare guidelines?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Please read the aftercare guidelines provided to you before answering.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>yes</t>
@@ -561,20 +569,24 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>i_agree_to_follow_tattoo_aftercare_guidelines</t>
+          <t>follow_aftercare_guidelines</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>i_agree_to_follow_tattoo_aftercare_guidelines</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Do you agree to follow tattoo aftercare guidelines?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Please check this box to confirm you agree to follow the aftercare guidelines.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>yes</t>
@@ -584,20 +596,24 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>i_agree_to_be_responsible_for_tattoo_care</t>
+          <t>responsible_for_tattoo_care</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>i_agree_to_be_responsible_for_tattoo_care</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Do you agree to be responsible for tattoo care?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Please check this box to confirm you agree to be responsible for tattoo care.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>yes</t>
@@ -607,22 +623,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>tattoo_care_info_source</t>
+          <t>receive_tattoo_care_info</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>how_did_you_receieve_tattoo_care_info</t>
+          <t>How did you receive tattoo care information?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>If not from an artist, please let us know how you received this information</t>
+          <t>Select one of the options below.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -644,7 +660,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>tattoo_type</t>
+          <t>What type of tattoo is this?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -662,12 +678,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>tattoo_session_id</t>
+          <t>session_number</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>session_number</t>
+          <t>Session Number</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -685,12 +701,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>tattoo_session_date</t>
+          <t>session_date</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>session_date</t>
+          <t>Session Date</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -708,12 +724,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>tattoo_session_time</t>
+          <t>session_time</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>session_time</t>
+          <t>Session Time</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -736,7 +752,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>client_id</t>
+          <t>Client ID</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -759,7 +775,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>artist_id</t>
+          <t>Artist ID</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -782,7 +798,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>parent_id</t>
+          <t>Parent ID</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -805,7 +821,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>tattoo_location</t>
+          <t>Tattoo Location</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -828,7 +844,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>tattoo_size</t>
+          <t>Tattoo Size</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -851,7 +867,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>tattoo_orientation</t>
+          <t>Tattoo Orientation</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -874,7 +890,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>tattoo_color</t>
+          <t>Tattoo Color</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -897,7 +913,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>tattoo_design</t>
+          <t>Tattoo Design</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -920,7 +936,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>tattoo_theme</t>
+          <t>Tattoo Theme</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -943,7 +959,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>tattoo_style</t>
+          <t>Tattoo Style</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -956,17 +972,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>tattoo_session_number</t>
+          <t>session_notes</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>session_number</t>
+          <t>Session Notes</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -979,17 +995,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>tattoo_session_date</t>
+          <t>tattoo_session_number</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>session_date</t>
+          <t>Tattoo Session Number</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1002,17 +1018,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>tattoo_session_time</t>
+          <t>tattoo_session_date</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>session_time</t>
+          <t>Tattoo Session Date</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1030,12 +1046,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>tattoo_session_duration</t>
+          <t>tattoo_session_time</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>session_duration</t>
+          <t>Tattoo Session Time</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1048,17 +1064,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>tattoo_session_notes</t>
+          <t>tattoo_session_duration</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>session_notes</t>
+          <t>Session Duration</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1081,7 +1097,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>aftercare_instructions</t>
+          <t>Aftercare Instructions</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1102,10 +1118,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="41" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1130,627 +1146,525 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>tattoo_aftercare_guidelines_acknowledgment_choices</t>
+          <t>understand_aftercare_guidelines_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>client</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Client</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>tattoo_aftercare_guidelines_acknowledgment_choices</t>
+          <t>understand_aftercare_guidelines_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>artist</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Artist</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>tattoo_aftercare_guidelines_acknowledgment_choices</t>
+          <t>receive_tattoo_care_info_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>parent/_guardian</t>
+          <t>from_an_artist</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Parent/ Guardian</t>
+          <t>From an artist</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>i_understand_tattoo_aftercare_guidelines_choices</t>
+          <t>receive_tattoo_care_info_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>i_understand_tattoo_aftercare_guidelines_choices</t>
+          <t>receive_tattoo_care_info_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>from_a_parent</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>From a parent</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>i_agree_to_be_responsible_for_tattoo_care_choices</t>
+          <t>tattoo_type_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>hand-drawn_tattoo</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Hand-Drawn Tattoo</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>i_agree_to_be_responsible_for_tattoo_care_choices</t>
+          <t>tattoo_type_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>machine-artwork</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Machine-Artwork</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>tattoo_care_info_source_choices</t>
+          <t>tattoo_type_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>artist</t>
+          <t>combination</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Artist</t>
+          <t>Combination</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>tattoo_care_info_source_choices</t>
+          <t>tattoo_location_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>online</t>
+          <t>head</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Head</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>tattoo_care_info_source_choices</t>
+          <t>tattoo_location_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>parent</t>
+          <t>neck</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Parent</t>
+          <t>Neck</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>tattoo_care_info_source_choices</t>
+          <t>tattoo_location_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>arms</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Arms</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>tattoo_type_choices</t>
+          <t>tattoo_location_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hand-drawn_tattoo</t>
+          <t>legs</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Hand-Drawn Tattoo</t>
+          <t>Legs</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>tattoo_type_choices</t>
+          <t>tattoo_location_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>machine-artwork</t>
+          <t>back</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Machine-Artwork</t>
+          <t>Back</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>tattoo_type_choices</t>
+          <t>tattoo_size_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>combination</t>
+          <t>small</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Combination</t>
+          <t>Small</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>tattoo_location_choices</t>
+          <t>tattoo_size_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>head</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Head</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>tattoo_location_choices</t>
+          <t>tattoo_size_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>neck</t>
+          <t>large</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Neck</t>
+          <t>Large</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>tattoo_location_choices</t>
+          <t>tattoo_orientation_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>arms</t>
+          <t>horizontal</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Arms</t>
+          <t>Horizontal</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>tattoo_location_choices</t>
+          <t>tattoo_orientation_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>legs</t>
+          <t>vertical</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Legs</t>
+          <t>Vertical</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>tattoo_location_choices</t>
+          <t>tattoo_orientation_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>back</t>
+          <t>rotating</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Back</t>
+          <t>Rotating</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>tattoo_size_choices</t>
+          <t>tattoo_color_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>red</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Small</t>
+          <t>Red</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>tattoo_size_choices</t>
+          <t>tattoo_color_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Blue</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>tattoo_size_choices</t>
+          <t>tattoo_color_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>large</t>
+          <t>green</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>Green</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>tattoo_orientation_choices</t>
+          <t>tattoo_design_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>horizontal</t>
+          <t>realistic</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Horizontal</t>
+          <t>Realistic</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>tattoo_orientation_choices</t>
+          <t>tattoo_design_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>vertical</t>
+          <t>abstract</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Vertical</t>
+          <t>Abstract</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>tattoo_orientation_choices</t>
+          <t>tattoo_design_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>rotating</t>
+          <t>geometric</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Rotating</t>
+          <t>Geometric</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>tattoo_color_choices</t>
+          <t>tattoo_theme_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>black_and_white</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Black and White</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>tattoo_color_choices</t>
+          <t>tattoo_theme_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>blue</t>
+          <t>color</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Color</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>tattoo_color_choices</t>
+          <t>tattoo_theme_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>neon</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Neon</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>tattoo_design_choices</t>
+          <t>tattoo_style_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>realistic</t>
+          <t>line_art</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Realistic</t>
+          <t>Line Art</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>tattoo_design_choices</t>
+          <t>tattoo_style_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>abstract</t>
+          <t>dot_work</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Abstract</t>
+          <t>Dot work</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>tattoo_design_choices</t>
+          <t>tattoo_style_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>geometric</t>
+          <t>color_fill</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
-        <is>
-          <t>Geometric</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>tattoo_theme_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>black_and_white</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Black and White</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>tattoo_theme_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>color</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Color</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>tattoo_theme_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>neon</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Neon</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>tattoo_style_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>line_art</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Line Art</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>tattoo_style_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>dot_work</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Dot work</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>tattoo_style_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>color_fill</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
         <is>
           <t>Color Fill</t>
         </is>
